--- a/811-Ticket-Report.xlsx
+++ b/811-Ticket-Report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="223">
   <si>
     <t>Ticket #</t>
   </si>
@@ -246,78 +246,6 @@
     <t>WINDHILL LN</t>
   </si>
   <si>
-    <t>26021005978</t>
-  </si>
-  <si>
-    <t>S CITATION DR</t>
-  </si>
-  <si>
-    <t>W RUFFIAN LN</t>
-  </si>
-  <si>
-    <t>INSIGHT COMMUNICATIONS (NEW ALBANY): Date:02/20/2026 07:59 AM Respondent:BENJAMIN GROSSMAN ( IN (USIC) ) Attempted to contact: RAFAEL RIVAS via Phone 4702622 | RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND: Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 20 | CENTERPOINT ENERGY (SOUTH): Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST  | CENTE</t>
-  </si>
-  <si>
-    <t>26021005983</t>
-  </si>
-  <si>
-    <t>W WHIRLAWAY DR</t>
-  </si>
-  <si>
-    <t>26021005984</t>
-  </si>
-  <si>
-    <t>COUNT FLEET DR</t>
-  </si>
-  <si>
-    <t>26021100001</t>
-  </si>
-  <si>
-    <t>FOXMOOR DR</t>
-  </si>
-  <si>
-    <t>BRANDYWINE DR</t>
-  </si>
-  <si>
-    <t>03/03/2026</t>
-  </si>
-  <si>
-    <t>26021100002</t>
-  </si>
-  <si>
-    <t>GLENNBROOKE DR</t>
-  </si>
-  <si>
-    <t>26021100003</t>
-  </si>
-  <si>
-    <t>26021100004</t>
-  </si>
-  <si>
-    <t>STONEGARDEN LN</t>
-  </si>
-  <si>
-    <t>26021100005</t>
-  </si>
-  <si>
-    <t>HAWTHORNE DR</t>
-  </si>
-  <si>
-    <t>26021100006</t>
-  </si>
-  <si>
-    <t>W GLENNBROOKE DR</t>
-  </si>
-  <si>
-    <t>26021100007</t>
-  </si>
-  <si>
-    <t>RUFFIAN LN</t>
-  </si>
-  <si>
-    <t>26021100010</t>
-  </si>
-  <si>
     <t>26021601665</t>
   </si>
   <si>
@@ -685,135 +613,6 @@
   </si>
   <si>
     <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:27 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:27 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>MARATHON PETROLEUM COMPANY, LLC</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:36 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:33 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:33 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:59 AM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:40 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:44 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:44 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:21 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:21 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:21 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:21 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/23/2026 05:01 AM AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:55 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:55 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:31 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:31 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:31 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:31 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:44 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 11:22 AM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:39 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:39 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:39 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:39 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 05:59 AM NEWBURGH, TOWN OF SEWER</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:46 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 12:33 PM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:46 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:46 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 05:55 AM NEWBURGH, TOWN OF SEWER</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:57 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:57 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:53 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:53 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 05:55 AM NEWBURGH, TOWN OF SEWER AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:08 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:00 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:00 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:00 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:00 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:22 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:08 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:08 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:34 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:34 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/16/2026 12:30 PM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:22 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:22 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 11:41 AM NEWBURGH, TOWN OF SEWER AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:55 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:55 CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:30 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:30 MAINSTREAM FIBER </t>
   </si>
   <si>
     <t>MARKED WITH EXCEPTIONS</t>
@@ -1346,7 +1145,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2418,14 +2217,14 @@
       <c r="A22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>17</v>
+      <c r="B22" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>20</v>
@@ -2437,45 +2236,45 @@
         <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="I22" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J22" s="2">
+        <v>3</v>
+      </c>
+      <c r="K22" s="2">
         <v>2</v>
       </c>
-      <c r="K22" s="2">
-        <v>3</v>
-      </c>
-      <c r="L22" s="4">
-        <v>5</v>
-      </c>
-      <c r="M22" s="2">
+      <c r="L22" s="2">
         <v>0</v>
+      </c>
+      <c r="M22" s="6">
+        <v>1</v>
       </c>
       <c r="N22" s="2">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>17</v>
+        <v>83</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>20</v>
@@ -2487,19 +2286,19 @@
         <v>22</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="I23" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J23" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="2">
-        <v>2</v>
-      </c>
-      <c r="L23" s="4">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -2508,24 +2307,24 @@
         <v>0</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>17</v>
+        <v>85</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>20</v>
@@ -2537,19 +2336,19 @@
         <v>22</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="I24" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J24" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2">
-        <v>1</v>
-      </c>
-      <c r="L24" s="4">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
@@ -2558,564 +2357,14 @@
         <v>0</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I25" s="2">
-        <v>10</v>
-      </c>
-      <c r="J25" s="2">
-        <v>2</v>
-      </c>
-      <c r="K25" s="2">
-        <v>3</v>
-      </c>
-      <c r="L25" s="4">
-        <v>5</v>
-      </c>
-      <c r="M25" s="2">
-        <v>0</v>
-      </c>
-      <c r="N25" s="2">
-        <v>0</v>
-      </c>
-      <c r="O25" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P25" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26" s="2">
-        <v>9</v>
-      </c>
-      <c r="J26" s="2">
-        <v>2</v>
-      </c>
-      <c r="K26" s="2">
-        <v>2</v>
-      </c>
-      <c r="L26" s="4">
-        <v>5</v>
-      </c>
-      <c r="M26" s="2">
-        <v>0</v>
-      </c>
-      <c r="N26" s="2">
-        <v>0</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I27" s="2">
-        <v>7</v>
-      </c>
-      <c r="J27" s="2">
-        <v>1</v>
-      </c>
-      <c r="K27" s="2">
-        <v>1</v>
-      </c>
-      <c r="L27" s="4">
-        <v>5</v>
-      </c>
-      <c r="M27" s="2">
-        <v>0</v>
-      </c>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I28" s="2">
-        <v>9</v>
-      </c>
-      <c r="J28" s="2">
-        <v>2</v>
-      </c>
-      <c r="K28" s="2">
-        <v>2</v>
-      </c>
-      <c r="L28" s="4">
-        <v>5</v>
-      </c>
-      <c r="M28" s="2">
-        <v>0</v>
-      </c>
-      <c r="N28" s="2">
-        <v>0</v>
-      </c>
-      <c r="O28" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I29" s="2">
-        <v>8</v>
-      </c>
-      <c r="J29" s="2">
-        <v>2</v>
-      </c>
-      <c r="K29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="4">
-        <v>5</v>
-      </c>
-      <c r="M29" s="2">
-        <v>0</v>
-      </c>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
-      <c r="O29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I30" s="2">
-        <v>8</v>
-      </c>
-      <c r="J30" s="2">
-        <v>2</v>
-      </c>
-      <c r="K30" s="2">
-        <v>1</v>
-      </c>
-      <c r="L30" s="4">
-        <v>5</v>
-      </c>
-      <c r="M30" s="2">
-        <v>0</v>
-      </c>
-      <c r="N30" s="2">
-        <v>0</v>
-      </c>
-      <c r="O30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I31" s="2">
-        <v>7</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
-      <c r="K31" s="2">
-        <v>2</v>
-      </c>
-      <c r="L31" s="4">
-        <v>4</v>
-      </c>
-      <c r="M31" s="2">
-        <v>0</v>
-      </c>
-      <c r="N31" s="2">
-        <v>0</v>
-      </c>
-      <c r="O31" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="P31" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32" s="2">
-        <v>8</v>
-      </c>
-      <c r="J32" s="2">
-        <v>2</v>
-      </c>
-      <c r="K32" s="2">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4">
-        <v>5</v>
-      </c>
-      <c r="M32" s="2">
-        <v>0</v>
-      </c>
-      <c r="N32" s="2">
-        <v>0</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I33" s="2">
-        <v>6</v>
-      </c>
-      <c r="J33" s="2">
-        <v>3</v>
-      </c>
-      <c r="K33" s="2">
-        <v>2</v>
-      </c>
-      <c r="L33" s="2">
-        <v>0</v>
-      </c>
-      <c r="M33" s="6">
-        <v>1</v>
-      </c>
-      <c r="N33" s="2">
-        <v>0</v>
-      </c>
-      <c r="O33" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I34" s="2">
-        <v>7</v>
-      </c>
-      <c r="J34" s="2">
-        <v>3</v>
-      </c>
-      <c r="K34" s="2">
-        <v>4</v>
-      </c>
-      <c r="L34" s="2">
-        <v>0</v>
-      </c>
-      <c r="M34" s="2">
-        <v>0</v>
-      </c>
-      <c r="N34" s="2">
-        <v>0</v>
-      </c>
-      <c r="O34" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="I35" s="2">
-        <v>7</v>
-      </c>
-      <c r="J35" s="2">
-        <v>4</v>
-      </c>
-      <c r="K35" s="2">
-        <v>3</v>
-      </c>
-      <c r="L35" s="2">
-        <v>0</v>
-      </c>
-      <c r="M35" s="2">
-        <v>0</v>
-      </c>
-      <c r="N35" s="2">
-        <v>0</v>
-      </c>
-      <c r="O35" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P24"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3123,7 +2372,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H279"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3150,16 +2399,16 @@
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>112</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3176,16 +2425,16 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3202,16 +2451,16 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3228,16 +2477,16 @@
         <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3254,16 +2503,16 @@
         <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3280,16 +2529,16 @@
         <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3306,16 +2555,16 @@
         <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>133</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3332,16 +2581,16 @@
         <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3358,16 +2607,16 @@
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3384,16 +2633,16 @@
         <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -3410,16 +2659,16 @@
         <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -3436,16 +2685,16 @@
         <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -3462,16 +2711,16 @@
         <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>140</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -3488,16 +2737,16 @@
         <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -3514,16 +2763,16 @@
         <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3540,16 +2789,16 @@
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3566,16 +2815,16 @@
         <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3592,16 +2841,16 @@
         <v>23</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G18" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -3618,16 +2867,16 @@
         <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -3644,16 +2893,16 @@
         <v>23</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -3670,16 +2919,16 @@
         <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -3696,16 +2945,16 @@
         <v>23</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -3722,16 +2971,16 @@
         <v>23</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -3748,16 +2997,16 @@
         <v>23</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -3774,16 +3023,16 @@
         <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>149</v>
+        <v>125</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3800,16 +3049,16 @@
         <v>23</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G26" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3826,16 +3075,16 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3852,16 +3101,16 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3878,16 +3127,16 @@
         <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G29" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G29" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3904,16 +3153,16 @@
         <v>23</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3930,16 +3179,16 @@
         <v>23</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3956,16 +3205,16 @@
         <v>23</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3982,16 +3231,16 @@
         <v>23</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -4008,16 +3257,16 @@
         <v>23</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G34" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H34" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -4034,16 +3283,16 @@
         <v>23</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -4060,16 +3309,16 @@
         <v>23</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -4086,16 +3335,16 @@
         <v>23</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>155</v>
+        <v>131</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -4112,16 +3361,16 @@
         <v>23</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -4138,16 +3387,16 @@
         <v>23</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -4164,16 +3413,16 @@
         <v>23</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>159</v>
+        <v>135</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -4190,16 +3439,16 @@
         <v>23</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -4216,16 +3465,16 @@
         <v>23</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G42" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H42" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -4242,16 +3491,16 @@
         <v>23</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -4268,16 +3517,16 @@
         <v>23</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -4294,16 +3543,16 @@
         <v>23</v>
       </c>
       <c r="E45" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G45" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G45" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -4320,16 +3569,16 @@
         <v>23</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -4346,16 +3595,16 @@
         <v>23</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>158</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -4372,16 +3621,16 @@
         <v>23</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -4398,16 +3647,16 @@
         <v>23</v>
       </c>
       <c r="E49" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G49" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G49" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -4424,16 +3673,16 @@
         <v>23</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -4450,16 +3699,16 @@
         <v>23</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G51" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -4476,16 +3725,16 @@
         <v>23</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -4502,16 +3751,16 @@
         <v>23</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -4528,16 +3777,16 @@
         <v>23</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>163</v>
+        <v>139</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -4554,16 +3803,16 @@
         <v>23</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -4580,16 +3829,16 @@
         <v>23</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -4606,16 +3855,16 @@
         <v>23</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G57" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -4632,16 +3881,16 @@
         <v>23</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -4658,16 +3907,16 @@
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G59" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -4684,16 +3933,16 @@
         <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -4710,16 +3959,16 @@
         <v>23</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>150</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -4736,16 +3985,16 @@
         <v>23</v>
       </c>
       <c r="E62" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H62" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4762,16 +4011,16 @@
         <v>23</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4788,16 +4037,16 @@
         <v>23</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4814,16 +4063,16 @@
         <v>23</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4840,16 +4089,16 @@
         <v>23</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4866,16 +4115,16 @@
         <v>23</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4892,16 +4141,16 @@
         <v>23</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4918,16 +4167,16 @@
         <v>23</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4944,16 +4193,16 @@
         <v>23</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4970,16 +4219,16 @@
         <v>23</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4996,16 +4245,16 @@
         <v>23</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -5022,16 +4271,16 @@
         <v>23</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F73" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G73" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -5048,16 +4297,16 @@
         <v>23</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -5074,16 +4323,16 @@
         <v>23</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -5100,16 +4349,16 @@
         <v>23</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -5126,16 +4375,16 @@
         <v>23</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -5152,16 +4401,16 @@
         <v>23</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -5178,16 +4427,16 @@
         <v>23</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -5204,16 +4453,16 @@
         <v>23</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -5230,16 +4479,16 @@
         <v>23</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -5256,16 +4505,16 @@
         <v>23</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -5282,16 +4531,16 @@
         <v>23</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -5308,16 +4557,16 @@
         <v>23</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -5334,16 +4583,16 @@
         <v>23</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -5360,16 +4609,16 @@
         <v>23</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -5386,16 +4635,16 @@
         <v>23</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -5412,16 +4661,16 @@
         <v>23</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -5438,16 +4687,16 @@
         <v>23</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -5464,16 +4713,16 @@
         <v>23</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>182</v>
+        <v>158</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -5490,16 +4739,16 @@
         <v>23</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -5516,16 +4765,16 @@
         <v>23</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -5542,16 +4791,16 @@
         <v>23</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -5568,16 +4817,16 @@
         <v>23</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -5594,16 +4843,16 @@
         <v>23</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -5620,16 +4869,16 @@
         <v>23</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -5646,16 +4895,16 @@
         <v>23</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -5672,16 +4921,16 @@
         <v>23</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>184</v>
+        <v>160</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -5698,16 +4947,16 @@
         <v>23</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -5724,16 +4973,16 @@
         <v>23</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -5750,16 +4999,16 @@
         <v>23</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>167</v>
+        <v>143</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -5776,16 +5025,16 @@
         <v>23</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -5802,16 +5051,16 @@
         <v>23</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -5828,16 +5077,16 @@
         <v>23</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -5854,16 +5103,16 @@
         <v>23</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>183</v>
+        <v>159</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -5880,16 +5129,16 @@
         <v>23</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -5906,16 +5155,16 @@
         <v>23</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -5932,16 +5181,16 @@
         <v>23</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>188</v>
+        <v>164</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -5958,16 +5207,16 @@
         <v>23</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>189</v>
+        <v>165</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -5984,16 +5233,16 @@
         <v>23</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>190</v>
+        <v>166</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -6010,16 +5259,16 @@
         <v>23</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -6036,16 +5285,16 @@
         <v>23</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -6062,16 +5311,16 @@
         <v>23</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -6088,16 +5337,16 @@
         <v>23</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>194</v>
+        <v>170</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -6114,16 +5363,16 @@
         <v>23</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -6140,16 +5389,16 @@
         <v>23</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>195</v>
+        <v>171</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -6166,16 +5415,16 @@
         <v>23</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -6192,16 +5441,16 @@
         <v>23</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>197</v>
+        <v>173</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -6218,16 +5467,16 @@
         <v>23</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>198</v>
+        <v>174</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -6244,16 +5493,16 @@
         <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -6270,16 +5519,16 @@
         <v>23</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -6296,16 +5545,16 @@
         <v>23</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -6322,16 +5571,16 @@
         <v>23</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G123" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -6348,16 +5597,16 @@
         <v>23</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -6374,16 +5623,16 @@
         <v>23</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>202</v>
+        <v>178</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -6400,16 +5649,16 @@
         <v>23</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -6426,16 +5675,16 @@
         <v>23</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>204</v>
+        <v>180</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -6452,16 +5701,16 @@
         <v>23</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>205</v>
+        <v>181</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -6478,16 +5727,16 @@
         <v>23</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -6504,16 +5753,16 @@
         <v>23</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>201</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -6530,16 +5779,16 @@
         <v>23</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G131" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H131" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H131" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -6556,16 +5805,16 @@
         <v>23</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -6582,16 +5831,16 @@
         <v>23</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>206</v>
+        <v>182</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -6608,16 +5857,16 @@
         <v>23</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -6634,16 +5883,16 @@
         <v>23</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>208</v>
+        <v>184</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -6660,16 +5909,16 @@
         <v>23</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -6686,16 +5935,16 @@
         <v>23</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>210</v>
+        <v>186</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -6712,16 +5961,16 @@
         <v>23</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>211</v>
+        <v>187</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -6738,16 +5987,16 @@
         <v>23</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>212</v>
+        <v>188</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -6764,16 +6013,16 @@
         <v>23</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G140" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H140" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H140" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -6790,16 +6039,16 @@
         <v>23</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -6816,16 +6065,16 @@
         <v>23</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -6842,16 +6091,16 @@
         <v>23</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -6868,16 +6117,16 @@
         <v>23</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>214</v>
+        <v>190</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -6894,16 +6143,16 @@
         <v>23</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>215</v>
+        <v>191</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -6920,16 +6169,16 @@
         <v>23</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -6946,16 +6195,16 @@
         <v>23</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -6972,16 +6221,16 @@
         <v>23</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -6998,16 +6247,16 @@
         <v>23</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -7024,16 +6273,16 @@
         <v>23</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -7050,16 +6299,16 @@
         <v>23</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -7076,16 +6325,16 @@
         <v>23</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -7102,16 +6351,16 @@
         <v>23</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -7128,16 +6377,16 @@
         <v>23</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -7154,16 +6403,16 @@
         <v>23</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -7180,16 +6429,16 @@
         <v>23</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -7206,16 +6455,16 @@
         <v>23</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -7232,16 +6481,16 @@
         <v>23</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -7258,16 +6507,16 @@
         <v>23</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -7284,16 +6533,16 @@
         <v>23</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -7310,16 +6559,16 @@
         <v>23</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>207</v>
+        <v>183</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -7336,16 +6585,16 @@
         <v>23</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -7362,16 +6611,16 @@
         <v>23</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -7388,16 +6637,16 @@
         <v>23</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>157</v>
+        <v>133</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -7414,16 +6663,16 @@
         <v>23</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -7440,16 +6689,16 @@
         <v>23</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>138</v>
+        <v>114</v>
       </c>
       <c r="G166" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H166" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H166" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -7457,25 +6706,25 @@
         <v>77</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>116</v>
+        <v>201</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -7483,25 +6732,25 @@
         <v>77</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>224</v>
+        <v>103</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>179</v>
+        <v>104</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>225</v>
+        <v>202</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -7509,25 +6758,25 @@
         <v>77</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>226</v>
+        <v>203</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -7535,25 +6784,25 @@
         <v>77</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>121</v>
+        <v>204</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>122</v>
+        <v>205</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>132</v>
+        <v>95</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -7561,25 +6810,25 @@
         <v>77</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>124</v>
+        <v>207</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G171" s="4" t="s">
-        <v>115</v>
+        <v>155</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -7587,74 +6836,74 @@
         <v>77</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G172" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>131</v>
+        <v>90</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>211</v>
@@ -7662,302 +6911,302 @@
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G175" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G176" s="4" t="s">
-        <v>115</v>
+        <v>107</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>139</v>
+        <v>213</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D177" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C177" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D177" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E177" s="2" t="s">
-        <v>113</v>
+        <v>204</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G177" s="4" t="s">
-        <v>115</v>
+        <v>205</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D178" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D178" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E178" s="2" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>179</v>
+        <v>155</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D179" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D179" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E179" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G179" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D180" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D180" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E180" s="2" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D181" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D181" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E181" s="2" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G181" s="4" t="s">
-        <v>115</v>
+        <v>101</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D182" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D182" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E182" s="2" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G182" s="4" t="s">
-        <v>115</v>
+        <v>104</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D183" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D183" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E183" s="2" t="s">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D184" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B184" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D184" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E184" s="2" t="s">
-        <v>134</v>
+        <v>204</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>135</v>
+        <v>205</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D185" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D185" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="E185" s="2" t="s">
-        <v>137</v>
+        <v>207</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G185" s="4" t="s">
-        <v>115</v>
+        <v>155</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>108</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>139</v>
+        <v>215</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>84</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>113</v>
@@ -7965,2433 +7214,15 @@
       <c r="F186" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G186" s="4" t="s">
-        <v>115</v>
+      <c r="G186" s="8" t="s">
+        <v>95</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G187" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G188" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H188" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G189" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H189" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G190" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H190" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G191" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G192" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G193" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G194" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H194" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G195" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H195" s="2" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G196" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G197" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G198" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H198" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G199" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H199" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G201" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H201" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G202" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G203" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G204" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H204" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G205" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G206" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H206" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G207" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G208" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G209" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G210" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G211" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H211" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G212" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G213" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G214" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G215" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G216" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H216" s="2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G217" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H217" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G218" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H218" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G219" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H219" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G220" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H220" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G221" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G222" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G223" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G224" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G225" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H225" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G226" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G227" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G228" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H228" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G229" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H229" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G230" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H230" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G231" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H231" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G232" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G233" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H233" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A234" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G234" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G235" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G236" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G237" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A238" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G238" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A239" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G239" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G240" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G241" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G242" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G243" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D244" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G244" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H244" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G245" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H245" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G246" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H246" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A247" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G247" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G248" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H248" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G249" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H249" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G250" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H250" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A251" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G251" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H251" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A252" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G252" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H252" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A253" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="G253" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H253" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A254" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G254" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H254" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A255" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G255" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H255" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G256" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H256" s="2" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G257" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H257" s="2" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G258" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A259" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G259" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="H259" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A260" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G260" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="H260" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D261" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G261" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H261" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G262" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H262" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A263" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G263" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H263" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A264" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G264" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H264" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A265" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G265" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H265" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G266" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H266" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A267" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G267" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H267" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G268" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H268" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G269" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H269" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G270" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G271" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H271" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G272" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H272" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A273" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G273" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H273" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G274" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H274" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="G275" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H275" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A276" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G276" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H276" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A277" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="G277" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H277" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A278" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G278" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="H278" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A279" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="G279" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="H279" s="2" t="s">
-        <v>288</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H279"/>
+  <autoFilter ref="A1:H186"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -10399,7 +7230,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -10427,7 +7258,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>289</v>
+        <v>222</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -10895,22 +7726,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>17</v>
-      </c>
       <c r="F22" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -10918,22 +7749,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>17</v>
+        <v>84</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="F23" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -10941,277 +7772,24 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>84</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>17</v>
+        <v>79</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>28</v>
       </c>
       <c r="F24" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="2">
-        <v>5</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="2">
-        <v>5</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F27" s="2">
-        <v>5</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="2">
-        <v>5</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="2">
-        <v>5</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="2">
-        <v>5</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="2">
-        <v>4</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="2">
-        <v>5</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="F33" s="2">
-        <v>0</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F34" s="2">
-        <v>0</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="F35" s="2">
-        <v>0</v>
-      </c>
-      <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
     </row>

--- a/811-Ticket-Report.xlsx
+++ b/811-Ticket-Report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="314">
   <si>
     <t>Ticket #</t>
   </si>
@@ -246,6 +246,102 @@
     <t>WINDHILL LN</t>
   </si>
   <si>
+    <t>26021005960</t>
+  </si>
+  <si>
+    <t>HILLSIDE DR</t>
+  </si>
+  <si>
+    <t>26021005962</t>
+  </si>
+  <si>
+    <t>26021005965</t>
+  </si>
+  <si>
+    <t>COUNT FLEET DR</t>
+  </si>
+  <si>
+    <t>W RUFFIAN LN</t>
+  </si>
+  <si>
+    <t>26021005968</t>
+  </si>
+  <si>
+    <t>S TRIPLE CROWN DR</t>
+  </si>
+  <si>
+    <t>INSIGHT COMMUNICATIONS (NEW ALBANY): Date:02/20/2026 07:59 AM Respondent:BENJAMIN GROSSMAN ( IN (USIC) ) Attempted to contact: RAFAEL RIVAS via Phone 4702622 | RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND: Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 20 | CENTERPOINT ENERGY (SOUTH): Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST  | CENTE</t>
+  </si>
+  <si>
+    <t>26021005973</t>
+  </si>
+  <si>
+    <t>S SECRETARIAT DR</t>
+  </si>
+  <si>
+    <t>26021005978</t>
+  </si>
+  <si>
+    <t>S CITATION DR</t>
+  </si>
+  <si>
+    <t>26021005983</t>
+  </si>
+  <si>
+    <t>W WHIRLAWAY DR</t>
+  </si>
+  <si>
+    <t>26021005984</t>
+  </si>
+  <si>
+    <t>26021100001</t>
+  </si>
+  <si>
+    <t>FOXMOOR DR</t>
+  </si>
+  <si>
+    <t>BRANDYWINE DR</t>
+  </si>
+  <si>
+    <t>03/03/2026</t>
+  </si>
+  <si>
+    <t>26021100002</t>
+  </si>
+  <si>
+    <t>GLENNBROOKE DR</t>
+  </si>
+  <si>
+    <t>26021100003</t>
+  </si>
+  <si>
+    <t>26021100004</t>
+  </si>
+  <si>
+    <t>STONEGARDEN LN</t>
+  </si>
+  <si>
+    <t>26021100005</t>
+  </si>
+  <si>
+    <t>HAWTHORNE DR</t>
+  </si>
+  <si>
+    <t>26021100006</t>
+  </si>
+  <si>
+    <t>W GLENNBROOKE DR</t>
+  </si>
+  <si>
+    <t>26021100007</t>
+  </si>
+  <si>
+    <t>RUFFIAN LN</t>
+  </si>
+  <si>
+    <t>26021100010</t>
+  </si>
+  <si>
     <t>26021601665</t>
   </si>
   <si>
@@ -613,6 +709,183 @@
   </si>
   <si>
     <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:27 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:27 CHANDLER UTILITIE</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:53 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:30 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 04:59 AM CENTERPOINT ENERGY (SOUTH) GAS</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:36 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:36 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:36 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:36 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/18/2026 09:22 AM AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:53 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:41 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:41 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:43 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:43 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:43 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:43 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:53 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:53 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:51 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:51 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:51 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:51 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:04 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:04 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:58 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:58 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:58 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:58 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:18 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:18 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:07 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:07 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:07 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:07 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>MARATHON PETROLEUM COMPANY, LLC</t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 04:36 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:33 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:33 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 04:40 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:44 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:44 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:21 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:21 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:21 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:21 CHANDLER UTILITIE</t>
+  </si>
+  <si>
+    <t>Date:02/23/2026 05:01 AM AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:55 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:55 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:31 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:31 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:31 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:31 CHANDLER UTILITIE</t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 04:44 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 11:22 AM CENTERPOINT ENERGY (SOUTH) GAS</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:39 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:39 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:39 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:39 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 05:59 AM NEWBURGH, TOWN OF SEWER</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:46 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 12:33 PM CENTERPOINT ENERGY (SOUTH) GAS</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:46 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:46 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 05:55 AM NEWBURGH, TOWN OF SEWER</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:57 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:57 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:53 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:53 CHANDLER UTILITIE</t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 05:55 AM NEWBURGH, TOWN OF SEWER AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:08 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:00 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:00 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:00 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:00 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:22 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:08 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:08 CHANDLER UTILITIE</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:34 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:34 IN AMERICAN WATER SEWER, WATER</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 CHANDLER UTILITIE</t>
+  </si>
+  <si>
+    <t>Date:02/16/2026 12:30 PM CENTERPOINT ENERGY (SOUTH) GAS</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:22 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:22 MAINSTREAM FIBER </t>
+  </si>
+  <si>
+    <t>Date:02/11/2026 11:41 AM NEWBURGH, TOWN OF SEWER AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:55 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:55 CENTERPOINT ENERGY (SOUTH) GAS</t>
+  </si>
+  <si>
+    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:30 CENTERPOINT ENERG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:30 MAINSTREAM FIBER </t>
   </si>
   <si>
     <t>MARKED WITH EXCEPTIONS</t>
@@ -1145,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2217,14 +2490,14 @@
       <c r="A22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>79</v>
-      </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>20</v>
@@ -2236,45 +2509,45 @@
         <v>22</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="I22" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J22" s="2">
+        <v>1</v>
+      </c>
+      <c r="K22" s="2">
         <v>3</v>
       </c>
-      <c r="K22" s="2">
-        <v>2</v>
-      </c>
-      <c r="L22" s="2">
+      <c r="L22" s="4">
+        <v>5</v>
+      </c>
+      <c r="M22" s="2">
         <v>0</v>
-      </c>
-      <c r="M22" s="6">
-        <v>1</v>
       </c>
       <c r="N22" s="2">
         <v>0</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>28</v>
+        <v>79</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>20</v>
@@ -2286,19 +2559,19 @@
         <v>22</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="I23" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J23" s="2">
+        <v>1</v>
+      </c>
+      <c r="K23" s="2">
         <v>3</v>
       </c>
-      <c r="K23" s="2">
-        <v>4</v>
-      </c>
-      <c r="L23" s="2">
-        <v>0</v>
+      <c r="L23" s="4">
+        <v>5</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -2307,24 +2580,24 @@
         <v>0</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>28</v>
+        <v>80</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>20</v>
@@ -2336,19 +2609,19 @@
         <v>22</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="I24" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J24" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K24" s="2">
-        <v>3</v>
-      </c>
-      <c r="L24" s="2">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="L24" s="4">
+        <v>5</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
@@ -2357,14 +2630,814 @@
         <v>0</v>
       </c>
       <c r="O24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" s="2">
+        <v>9</v>
+      </c>
+      <c r="J25" s="2">
+        <v>2</v>
+      </c>
+      <c r="K25" s="2">
+        <v>2</v>
+      </c>
+      <c r="L25" s="4">
+        <v>5</v>
+      </c>
+      <c r="M25" s="2">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2">
+        <v>0</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="2">
+        <v>9</v>
+      </c>
+      <c r="J26" s="2">
+        <v>2</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2</v>
+      </c>
+      <c r="L26" s="4">
+        <v>5</v>
+      </c>
+      <c r="M26" s="2">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2">
+        <v>0</v>
+      </c>
+      <c r="O26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I27" s="2">
+        <v>10</v>
+      </c>
+      <c r="J27" s="2">
+        <v>2</v>
+      </c>
+      <c r="K27" s="2">
+        <v>3</v>
+      </c>
+      <c r="L27" s="4">
+        <v>5</v>
+      </c>
+      <c r="M27" s="2">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2">
+        <v>0</v>
+      </c>
+      <c r="O27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I28" s="2">
+        <v>9</v>
+      </c>
+      <c r="J28" s="2">
+        <v>2</v>
+      </c>
+      <c r="K28" s="2">
+        <v>2</v>
+      </c>
+      <c r="L28" s="4">
+        <v>5</v>
+      </c>
+      <c r="M28" s="2">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I29" s="2">
+        <v>8</v>
+      </c>
+      <c r="J29" s="2">
+        <v>2</v>
+      </c>
+      <c r="K29" s="2">
+        <v>1</v>
+      </c>
+      <c r="L29" s="4">
+        <v>5</v>
+      </c>
+      <c r="M29" s="2">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2">
+        <v>0</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I30" s="2">
+        <v>10</v>
+      </c>
+      <c r="J30" s="2">
+        <v>2</v>
+      </c>
+      <c r="K30" s="2">
+        <v>3</v>
+      </c>
+      <c r="L30" s="4">
+        <v>5</v>
+      </c>
+      <c r="M30" s="2">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2">
+        <v>0</v>
+      </c>
+      <c r="O30" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P30" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I31" s="2">
+        <v>9</v>
+      </c>
+      <c r="J31" s="2">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2">
+        <v>2</v>
+      </c>
+      <c r="L31" s="4">
+        <v>5</v>
+      </c>
+      <c r="M31" s="2">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2">
+        <v>0</v>
+      </c>
+      <c r="O31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I32" s="2">
+        <v>7</v>
+      </c>
+      <c r="J32" s="2">
+        <v>1</v>
+      </c>
+      <c r="K32" s="2">
+        <v>1</v>
+      </c>
+      <c r="L32" s="4">
+        <v>5</v>
+      </c>
+      <c r="M32" s="2">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2">
+        <v>0</v>
+      </c>
+      <c r="O32" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I33" s="2">
+        <v>9</v>
+      </c>
+      <c r="J33" s="2">
+        <v>2</v>
+      </c>
+      <c r="K33" s="2">
+        <v>2</v>
+      </c>
+      <c r="L33" s="4">
+        <v>5</v>
+      </c>
+      <c r="M33" s="2">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2">
+        <v>0</v>
+      </c>
+      <c r="O33" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I34" s="2">
+        <v>8</v>
+      </c>
+      <c r="J34" s="2">
+        <v>2</v>
+      </c>
+      <c r="K34" s="2">
+        <v>1</v>
+      </c>
+      <c r="L34" s="4">
+        <v>5</v>
+      </c>
+      <c r="M34" s="2">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2">
+        <v>0</v>
+      </c>
+      <c r="O34" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I35" s="2">
+        <v>8</v>
+      </c>
+      <c r="J35" s="2">
+        <v>2</v>
+      </c>
+      <c r="K35" s="2">
+        <v>1</v>
+      </c>
+      <c r="L35" s="4">
+        <v>5</v>
+      </c>
+      <c r="M35" s="2">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2">
+        <v>0</v>
+      </c>
+      <c r="O35" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I36" s="2">
+        <v>7</v>
+      </c>
+      <c r="J36" s="2">
+        <v>1</v>
+      </c>
+      <c r="K36" s="2">
+        <v>2</v>
+      </c>
+      <c r="L36" s="4">
+        <v>4</v>
+      </c>
+      <c r="M36" s="2">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2">
+        <v>0</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I37" s="2">
+        <v>8</v>
+      </c>
+      <c r="J37" s="2">
+        <v>2</v>
+      </c>
+      <c r="K37" s="2">
+        <v>1</v>
+      </c>
+      <c r="L37" s="4">
+        <v>5</v>
+      </c>
+      <c r="M37" s="2">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2">
+        <v>0</v>
+      </c>
+      <c r="O37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P37" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I38" s="2">
+        <v>6</v>
+      </c>
+      <c r="J38" s="2">
+        <v>3</v>
+      </c>
+      <c r="K38" s="2">
+        <v>2</v>
+      </c>
+      <c r="L38" s="2">
+        <v>0</v>
+      </c>
+      <c r="M38" s="6">
+        <v>1</v>
+      </c>
+      <c r="N38" s="2">
+        <v>0</v>
+      </c>
+      <c r="O38" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P38" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I39" s="2">
+        <v>7</v>
+      </c>
+      <c r="J39" s="2">
+        <v>3</v>
+      </c>
+      <c r="K39" s="2">
+        <v>4</v>
+      </c>
+      <c r="L39" s="2">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2">
+        <v>0</v>
+      </c>
+      <c r="O39" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="P24" s="2" t="s">
+      <c r="P39" s="2" t="s">
         <v>30</v>
       </c>
     </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I40" s="2">
+        <v>7</v>
+      </c>
+      <c r="J40" s="2">
+        <v>4</v>
+      </c>
+      <c r="K40" s="2">
+        <v>3</v>
+      </c>
+      <c r="L40" s="2">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2">
+        <v>0</v>
+      </c>
+      <c r="O40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="P40" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P24"/>
+  <autoFilter ref="A1:P40"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -2372,7 +3445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H324"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2399,16 +3472,16 @@
         <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -2425,16 +3498,16 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -2451,16 +3524,16 @@
         <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2477,16 +3550,16 @@
         <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -2503,16 +3576,16 @@
         <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -2529,16 +3602,16 @@
         <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -2555,16 +3628,16 @@
         <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2581,16 +3654,16 @@
         <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2607,16 +3680,16 @@
         <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2633,16 +3706,16 @@
         <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2659,16 +3732,16 @@
         <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2685,16 +3758,16 @@
         <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>99</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2711,16 +3784,16 @@
         <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2737,16 +3810,16 @@
         <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2763,16 +3836,16 @@
         <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -2789,16 +3862,16 @@
         <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -2815,16 +3888,16 @@
         <v>23</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -2841,16 +3914,16 @@
         <v>23</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -2867,16 +3940,16 @@
         <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -2893,16 +3966,16 @@
         <v>23</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -2919,16 +3992,16 @@
         <v>23</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -2945,16 +4018,16 @@
         <v>23</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -2971,16 +4044,16 @@
         <v>23</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -2997,16 +4070,16 @@
         <v>23</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -3023,16 +4096,16 @@
         <v>23</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3049,16 +4122,16 @@
         <v>23</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3075,16 +4148,16 @@
         <v>23</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3101,16 +4174,16 @@
         <v>23</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3127,16 +4200,16 @@
         <v>23</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3153,16 +4226,16 @@
         <v>23</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3179,16 +4252,16 @@
         <v>23</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3205,16 +4278,16 @@
         <v>23</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3231,16 +4304,16 @@
         <v>23</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -3257,16 +4330,16 @@
         <v>23</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3283,16 +4356,16 @@
         <v>23</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3309,16 +4382,16 @@
         <v>23</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3335,16 +4408,16 @@
         <v>23</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3361,16 +4434,16 @@
         <v>23</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3387,16 +4460,16 @@
         <v>23</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -3413,16 +4486,16 @@
         <v>23</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>135</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3439,16 +4512,16 @@
         <v>23</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3465,16 +4538,16 @@
         <v>23</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3491,16 +4564,16 @@
         <v>23</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3517,16 +4590,16 @@
         <v>23</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3543,16 +4616,16 @@
         <v>23</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3569,16 +4642,16 @@
         <v>23</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3595,16 +4668,16 @@
         <v>23</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3621,16 +4694,16 @@
         <v>23</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -3647,16 +4720,16 @@
         <v>23</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -3673,16 +4746,16 @@
         <v>23</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -3699,16 +4772,16 @@
         <v>23</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -3725,16 +4798,16 @@
         <v>23</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -3751,16 +4824,16 @@
         <v>23</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -3777,16 +4850,16 @@
         <v>23</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -3803,16 +4876,16 @@
         <v>23</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -3829,16 +4902,16 @@
         <v>23</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -3855,16 +4928,16 @@
         <v>23</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -3881,16 +4954,16 @@
         <v>23</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -3907,16 +4980,16 @@
         <v>23</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>119</v>
+        <v>151</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -3933,16 +5006,16 @@
         <v>23</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -3959,16 +5032,16 @@
         <v>23</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>126</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -3985,16 +5058,16 @@
         <v>23</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>127</v>
+        <v>159</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -4011,16 +5084,16 @@
         <v>23</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -4037,16 +5110,16 @@
         <v>23</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -4063,16 +5136,16 @@
         <v>23</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>142</v>
+        <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -4089,16 +5162,16 @@
         <v>23</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -4115,16 +5188,16 @@
         <v>23</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -4141,16 +5214,16 @@
         <v>23</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -4167,16 +5240,16 @@
         <v>23</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -4193,16 +5266,16 @@
         <v>23</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -4219,16 +5292,16 @@
         <v>23</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -4245,16 +5318,16 @@
         <v>23</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>147</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -4271,16 +5344,16 @@
         <v>23</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -4297,16 +5370,16 @@
         <v>23</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>148</v>
+        <v>180</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -4323,16 +5396,16 @@
         <v>23</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -4349,16 +5422,16 @@
         <v>23</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -4375,16 +5448,16 @@
         <v>23</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -4401,16 +5474,16 @@
         <v>23</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -4427,16 +5500,16 @@
         <v>23</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -4453,16 +5526,16 @@
         <v>23</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
@@ -4479,16 +5552,16 @@
         <v>23</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>151</v>
+        <v>183</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -4505,16 +5578,16 @@
         <v>23</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -4531,16 +5604,16 @@
         <v>23</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -4557,16 +5630,16 @@
         <v>23</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -4583,16 +5656,16 @@
         <v>23</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -4609,16 +5682,16 @@
         <v>23</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -4635,16 +5708,16 @@
         <v>23</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -4661,16 +5734,16 @@
         <v>23</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>156</v>
+        <v>188</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -4687,16 +5760,16 @@
         <v>23</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>157</v>
+        <v>189</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -4713,16 +5786,16 @@
         <v>23</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -4739,16 +5812,16 @@
         <v>23</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -4765,16 +5838,16 @@
         <v>23</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -4791,16 +5864,16 @@
         <v>23</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -4817,16 +5890,16 @@
         <v>23</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -4843,16 +5916,16 @@
         <v>23</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>122</v>
+        <v>154</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -4869,16 +5942,16 @@
         <v>23</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -4895,16 +5968,16 @@
         <v>23</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -4921,16 +5994,16 @@
         <v>23</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>160</v>
+        <v>192</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -4947,16 +6020,16 @@
         <v>23</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -4973,16 +6046,16 @@
         <v>23</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -4999,16 +6072,16 @@
         <v>23</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>143</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -5025,16 +6098,16 @@
         <v>23</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -5051,16 +6124,16 @@
         <v>23</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -5077,16 +6150,16 @@
         <v>23</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H104" s="2" t="s">
-        <v>150</v>
+        <v>182</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -5103,16 +6176,16 @@
         <v>23</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -5129,16 +6202,16 @@
         <v>23</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>162</v>
+        <v>194</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -5155,16 +6228,16 @@
         <v>23</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>163</v>
+        <v>195</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -5181,16 +6254,16 @@
         <v>23</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>164</v>
+        <v>196</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -5207,16 +6280,16 @@
         <v>23</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -5233,16 +6306,16 @@
         <v>23</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>166</v>
+        <v>198</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -5259,16 +6332,16 @@
         <v>23</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>167</v>
+        <v>199</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -5285,16 +6358,16 @@
         <v>23</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>168</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -5311,16 +6384,16 @@
         <v>23</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>154</v>
+        <v>186</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -5337,16 +6410,16 @@
         <v>23</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H114" s="2" t="s">
-        <v>170</v>
+        <v>202</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -5363,16 +6436,16 @@
         <v>23</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H115" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -5389,16 +6462,16 @@
         <v>23</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>171</v>
+        <v>203</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -5415,16 +6488,16 @@
         <v>23</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H117" s="2" t="s">
-        <v>172</v>
+        <v>204</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -5441,16 +6514,16 @@
         <v>23</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>173</v>
+        <v>205</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -5467,16 +6540,16 @@
         <v>23</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>174</v>
+        <v>206</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -5493,16 +6566,16 @@
         <v>23</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -5519,16 +6592,16 @@
         <v>23</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -5545,16 +6618,16 @@
         <v>23</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -5571,16 +6644,16 @@
         <v>23</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -5597,16 +6670,16 @@
         <v>23</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -5623,16 +6696,16 @@
         <v>23</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -5649,16 +6722,16 @@
         <v>23</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -5675,16 +6748,16 @@
         <v>23</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>180</v>
+        <v>212</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -5701,16 +6774,16 @@
         <v>23</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>181</v>
+        <v>213</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -5727,16 +6800,16 @@
         <v>23</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H129" s="2" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -5753,16 +6826,16 @@
         <v>23</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>177</v>
+        <v>209</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -5779,16 +6852,16 @@
         <v>23</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H131" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -5805,16 +6878,16 @@
         <v>23</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -5831,16 +6904,16 @@
         <v>23</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>182</v>
+        <v>214</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
@@ -5857,16 +6930,16 @@
         <v>23</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
@@ -5883,16 +6956,16 @@
         <v>23</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>184</v>
+        <v>216</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
@@ -5909,16 +6982,16 @@
         <v>23</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>185</v>
+        <v>217</v>
       </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.25">
@@ -5935,16 +7008,16 @@
         <v>23</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>186</v>
+        <v>218</v>
       </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
@@ -5961,16 +7034,16 @@
         <v>23</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H138" s="2" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.25">
@@ -5987,16 +7060,16 @@
         <v>23</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H139" s="2" t="s">
-        <v>188</v>
+        <v>220</v>
       </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
@@ -6013,16 +7086,16 @@
         <v>23</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H140" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -6039,16 +7112,16 @@
         <v>23</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H141" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -6065,16 +7138,16 @@
         <v>23</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H142" s="2" t="s">
-        <v>189</v>
+        <v>221</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -6091,16 +7164,16 @@
         <v>23</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H143" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -6117,16 +7190,16 @@
         <v>23</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H144" s="2" t="s">
-        <v>190</v>
+        <v>222</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -6143,16 +7216,16 @@
         <v>23</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H145" s="2" t="s">
-        <v>191</v>
+        <v>223</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -6169,16 +7242,16 @@
         <v>23</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H146" s="2" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -6195,16 +7268,16 @@
         <v>23</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -6221,16 +7294,16 @@
         <v>23</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H148" s="2" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -6247,16 +7320,16 @@
         <v>23</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H149" s="2" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.25">
@@ -6273,16 +7346,16 @@
         <v>23</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H150" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
@@ -6299,16 +7372,16 @@
         <v>23</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H151" s="2" t="s">
-        <v>194</v>
+        <v>226</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -6325,16 +7398,16 @@
         <v>23</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G152" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H152" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -6351,16 +7424,16 @@
         <v>23</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H153" s="2" t="s">
-        <v>195</v>
+        <v>227</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -6377,16 +7450,16 @@
         <v>23</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H154" s="2" t="s">
-        <v>196</v>
+        <v>228</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
@@ -6403,16 +7476,16 @@
         <v>23</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H155" s="2" t="s">
-        <v>175</v>
+        <v>207</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.25">
@@ -6429,16 +7502,16 @@
         <v>23</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H156" s="2" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.25">
@@ -6455,16 +7528,16 @@
         <v>23</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H157" s="2" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
@@ -6481,16 +7554,16 @@
         <v>23</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H158" s="2" t="s">
-        <v>193</v>
+        <v>225</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -6507,16 +7580,16 @@
         <v>23</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>89</v>
+        <v>121</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H159" s="2" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -6533,16 +7606,16 @@
         <v>23</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H160" s="2" t="s">
-        <v>197</v>
+        <v>229</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
@@ -6559,16 +7632,16 @@
         <v>23</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>97</v>
+        <v>129</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>98</v>
+        <v>130</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H161" s="2" t="s">
-        <v>183</v>
+        <v>215</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.25">
@@ -6585,16 +7658,16 @@
         <v>23</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>100</v>
+        <v>132</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H162" s="2" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -6611,16 +7684,16 @@
         <v>23</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H163" s="2" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -6637,16 +7710,16 @@
         <v>23</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H164" s="2" t="s">
-        <v>176</v>
+        <v>208</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -6663,16 +7736,16 @@
         <v>23</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H165" s="2" t="s">
-        <v>192</v>
+        <v>224</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -6689,16 +7762,16 @@
         <v>23</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="H166" s="2" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
@@ -6706,25 +7779,25 @@
         <v>77</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G167" s="6" t="s">
-        <v>200</v>
+        <v>122</v>
+      </c>
+      <c r="G167" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>201</v>
+        <v>124</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
@@ -6732,25 +7805,25 @@
         <v>77</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G168" s="8" t="s">
-        <v>95</v>
+        <v>126</v>
+      </c>
+      <c r="G168" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>202</v>
+        <v>232</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
@@ -6758,25 +7831,25 @@
         <v>77</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>106</v>
+        <v>129</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>107</v>
+        <v>130</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>203</v>
+        <v>233</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
@@ -6784,25 +7857,25 @@
         <v>77</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>204</v>
+        <v>132</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G170" s="8" t="s">
-        <v>95</v>
+        <v>133</v>
+      </c>
+      <c r="G170" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -6810,25 +7883,25 @@
         <v>77</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>207</v>
+        <v>135</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G171" s="8" t="s">
-        <v>108</v>
+        <v>136</v>
+      </c>
+      <c r="G171" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>208</v>
+        <v>235</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -6836,393 +7909,3981 @@
         <v>77</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="G175" s="8" t="s">
-        <v>95</v>
+        <v>146</v>
+      </c>
+      <c r="G175" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>212</v>
+        <v>147</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G176" s="8" t="s">
-        <v>108</v>
+        <v>122</v>
+      </c>
+      <c r="G176" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>213</v>
+        <v>124</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>204</v>
+        <v>125</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G177" s="8" t="s">
-        <v>95</v>
+        <v>126</v>
+      </c>
+      <c r="G177" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>207</v>
+        <v>129</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>108</v>
+        <v>140</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G179" s="8" t="s">
-        <v>108</v>
+        <v>133</v>
+      </c>
+      <c r="G179" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G180" s="8" t="s">
-        <v>108</v>
+        <v>136</v>
+      </c>
+      <c r="G180" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>104</v>
+        <v>165</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>106</v>
+        <v>142</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="G184" s="8" t="s">
-        <v>95</v>
+        <v>146</v>
+      </c>
+      <c r="G184" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>214</v>
+        <v>147</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>207</v>
+        <v>121</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G185" s="8" t="s">
-        <v>108</v>
+        <v>122</v>
+      </c>
+      <c r="G185" s="4" t="s">
+        <v>123</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>215</v>
+        <v>124</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G186" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G188" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G189" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G193" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B194" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C186" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D186" s="2" t="s">
+      <c r="C194" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G194" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G195" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G197" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G198" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G202" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G203" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G204" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G206" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G207" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H209" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H210" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G211" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H211" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G212" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H212" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H213" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H214" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H215" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H216" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H217" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H218" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H219" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H220" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G221" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H221" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G222" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H222" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H223" s="2" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G224" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H224" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H225" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G226" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H226" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G227" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H227" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H228" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H229" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G230" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H230" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B231" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="C231" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G231" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H231" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G232" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H232" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H233" s="2" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G234" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H234" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G235" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H235" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H236" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H237" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G238" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H238" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G239" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H239" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H240" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G241" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H241" s="2" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H242" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G243" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H243" s="2" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G244" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H244" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H245" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H246" s="2" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H247" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G248" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H248" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G249" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H249" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G250" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H250" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H251" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G252" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H252" s="2" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G253" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H253" s="2" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H254" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H255" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H256" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G257" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H257" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G258" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H258" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G259" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H259" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G261" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H261" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G262" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H262" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H263" s="2" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G264" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G265" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H265" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G266" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H266" s="2" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H267" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G268" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H268" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G269" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H269" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H270" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F271" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H271" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F272" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H272" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F273" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G273" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H273" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F274" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G274" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H274" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G275" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H275" s="2" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H276" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G277" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H277" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G278" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H278" s="2" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A279" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B279" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C279" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H279" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A280" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H280" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A281" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G281" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H281" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G282" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H282" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B283" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C283" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F283" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G283" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H283" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A284" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B284" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C284" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="F284" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G284" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H284" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A285" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B285" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C285" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F285" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G285" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H285" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A286" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B286" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C286" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F286" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G286" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H286" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A287" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B287" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C287" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F287" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G287" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H287" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B288" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F288" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G288" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H288" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A289" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B289" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F289" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G289" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H289" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F290" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G290" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H290" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A291" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B291" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C291" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F291" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G291" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H291" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A292" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B292" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C292" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F292" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G292" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H292" s="2" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G293" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H293" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A294" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F294" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G294" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H294" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F295" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G295" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H295" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F296" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H296" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F297" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G297" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H297" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F298" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G298" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H298" s="2" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F299" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G299" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H299" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F300" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G300" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H300" s="2" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F301" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G301" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H301" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F302" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="G302" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H302" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F303" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H303" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F304" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G304" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H304" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A305" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B305" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C305" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D305" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F186" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="G186" s="8" t="s">
-        <v>95</v>
-      </c>
-      <c r="H186" s="2" t="s">
-        <v>221</v>
+      <c r="E305" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F305" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G305" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H305" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A306" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F306" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H306" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A307" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F307" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H307" s="2" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A308" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F308" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H308" s="2" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A309" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B309" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F309" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H309" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A310" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B310" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C310" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F310" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H310" s="2" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A311" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B311" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C311" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F311" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H311" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C312" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F312" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H312" s="2" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F313" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H313" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A314" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F314" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H314" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A315" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B315" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C315" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F315" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G315" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H315" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A316" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B316" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C316" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F316" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H316" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F317" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H317" s="2" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A318" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B318" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C318" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F318" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="G318" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H318" s="2" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A319" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B319" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C319" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F319" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G319" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H319" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A320" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B320" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C320" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F320" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G320" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H320" s="2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B321" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C321" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F321" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G321" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H321" s="2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A322" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B322" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C322" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F322" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="G322" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H322" s="2" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A323" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B323" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C323" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F323" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="G323" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="H323" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A324" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B324" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C324" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F324" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G324" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H324" s="2" t="s">
+        <v>312</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H186"/>
+  <autoFilter ref="A1:H324"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -7230,7 +11891,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -7258,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>222</v>
+        <v>313</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -7726,22 +12387,22 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -7749,22 +12410,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>28</v>
+        <v>61</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -7772,24 +12433,392 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" s="8" t="s">
+      <c r="D25" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F25" s="2">
+        <v>5</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" s="2">
+        <v>5</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F27" s="2">
+        <v>5</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="2">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F29" s="2">
+        <v>5</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F30" s="2">
+        <v>5</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F31" s="2">
+        <v>5</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="2">
+        <v>5</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33" s="2">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="2">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="2">
+        <v>5</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F36" s="2">
+        <v>4</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F37" s="2">
+        <v>5</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="2">
+        <v>0</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F39" s="2">
         <v>0</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G39" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F40" s="2">
+        <v>0</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>20</v>
       </c>
     </row>

--- a/811-Ticket-Report.xlsx
+++ b/811-Ticket-Report.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3239" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="255">
   <si>
     <t>Ticket #</t>
   </si>
@@ -249,6 +249,9 @@
     <t>26021005960</t>
   </si>
   <si>
+    <t>UNKNOWN</t>
+  </si>
+  <si>
     <t>HILLSIDE DR</t>
   </si>
   <si>
@@ -270,9 +273,6 @@
     <t>S TRIPLE CROWN DR</t>
   </si>
   <si>
-    <t>INSIGHT COMMUNICATIONS (NEW ALBANY): Date:02/20/2026 07:59 AM Respondent:BENJAMIN GROSSMAN ( IN (USIC) ) Attempted to contact: RAFAEL RIVAS via Phone 4702622 | RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND: Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 20 | CENTERPOINT ENERGY (SOUTH): Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST  | CENTE</t>
-  </si>
-  <si>
     <t>26021005973</t>
   </si>
   <si>
@@ -709,183 +709,6 @@
   </si>
   <si>
     <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:27 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:27 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:53 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:30 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:59 AM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:36 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:36 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:36 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:36 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/18/2026 09:22 AM AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:53 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:41 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:41 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:43 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:43 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:43 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:43 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:53 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:53 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:51 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:51 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:51 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:51 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:04 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:04 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:58 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:58 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:58 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:58 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:18 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:18 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:07 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:07 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:07 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:07 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>MARATHON PETROLEUM COMPANY, LLC</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:36 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:33 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:33 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:40 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:44 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:44 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:21 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:21 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:21 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:21 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/23/2026 05:01 AM AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:55 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:55 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:31 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:31 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:31 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:31 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 04:44 AM Respondent:HANNAH MCMILLEN RCN TELECOM SERVICES OF ILLINOIS, LLC DBA ASTOUND BROADBAND CABLE TV, COMMUNICATIONS, FIBER OPTIC</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 11:22 AM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:39 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:39 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:39 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:39 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 05:59 AM NEWBURGH, TOWN OF SEWER</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:46 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 12:33 PM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:46 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:46 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:46 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 05:55 AM NEWBURGH, TOWN OF SEWER</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:57 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:57 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:53 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:53 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:53 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 05:55 AM NEWBURGH, TOWN OF SEWER AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:08 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:00 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:00 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:00 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:00 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:22 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:08 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:08 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:08 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:34 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:34 IN AMERICAN WATER SEWER, WATER</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:14 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:14 CHANDLER UTILITIE</t>
-  </si>
-  <si>
-    <t>Date:02/16/2026 12:30 PM CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:22 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:22 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:22 MAINSTREAM FIBER </t>
-  </si>
-  <si>
-    <t>Date:02/11/2026 11:41 AM NEWBURGH, TOWN OF SEWER AT&amp;T - DISTRIBUTION COMMUNICATIONS</t>
-  </si>
-  <si>
-    <t>Date:02/12/2026 08:58 AM Attempted to contact: RAFAEL RIVAS, Comments : RAFAEL - CHANGED FROM: 2026-02-13 06:00:00 TO 2026-03-02 06:00:55 - EXCAVATION DATE CHANGED FROM: 2026-02-13 07:00:00 TO: 2026-03-02 07:00:55 CENTERPOINT ENERGY (SOUTH) GAS</t>
-  </si>
-  <si>
-    <t>Date:02/19/2026 01:02 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:30 CENTERPOINT ENERG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date:02/19/2026 01:03 PM Respondent:OTS LOCATING Attempted to contact: RAFAEL RIVAS, Comments : NATHAN. PRIORITIES LIST ALREADY GIVEN BY CONTRACTOR - CHANGED FROM: 2026-02-20 06:00:45 TO 2026-02-27 06:00:30 - EXCAVATION DATE CHANGED FROM: 2026-02-20 07:00:45 TO: 2026-02-27 07:00:30 MAINSTREAM FIBER </t>
   </si>
   <si>
     <t>MARKED WITH EXCEPTIONS</t>
@@ -2490,11 +2313,11 @@
       <c r="A22" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>17</v>
+      <c r="B22" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>61</v>
@@ -2512,16 +2335,16 @@
         <v>23</v>
       </c>
       <c r="I22" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2">
-        <v>3</v>
-      </c>
-      <c r="L22" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="2">
+        <v>0</v>
       </c>
       <c r="M22" s="2">
         <v>0</v>
@@ -2530,21 +2353,21 @@
         <v>0</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>61</v>
@@ -2562,16 +2385,16 @@
         <v>23</v>
       </c>
       <c r="I23" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J23" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2">
-        <v>3</v>
-      </c>
-      <c r="L23" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L23" s="2">
+        <v>0</v>
       </c>
       <c r="M23" s="2">
         <v>0</v>
@@ -2580,24 +2403,24 @@
         <v>0</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>17</v>
+        <v>81</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>20</v>
@@ -2612,16 +2435,16 @@
         <v>23</v>
       </c>
       <c r="I24" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J24" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2">
-        <v>2</v>
-      </c>
-      <c r="L24" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L24" s="2">
+        <v>0</v>
       </c>
       <c r="M24" s="2">
         <v>0</v>
@@ -2630,24 +2453,24 @@
         <v>0</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>20</v>
@@ -2662,16 +2485,16 @@
         <v>23</v>
       </c>
       <c r="I25" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J25" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2">
-        <v>2</v>
-      </c>
-      <c r="L25" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L25" s="2">
+        <v>0</v>
       </c>
       <c r="M25" s="2">
         <v>0</v>
@@ -2680,24 +2503,24 @@
         <v>0</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>17</v>
+      <c r="B26" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>87</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>20</v>
@@ -2712,16 +2535,16 @@
         <v>23</v>
       </c>
       <c r="I26" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J26" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2">
-        <v>2</v>
-      </c>
-      <c r="L26" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L26" s="2">
+        <v>0</v>
       </c>
       <c r="M26" s="2">
         <v>0</v>
@@ -2730,24 +2553,24 @@
         <v>0</v>
       </c>
       <c r="O26" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>17</v>
+      <c r="B27" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>89</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>20</v>
@@ -2762,16 +2585,16 @@
         <v>23</v>
       </c>
       <c r="I27" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J27" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K27" s="2">
-        <v>3</v>
-      </c>
-      <c r="L27" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L27" s="2">
+        <v>0</v>
       </c>
       <c r="M27" s="2">
         <v>0</v>
@@ -2780,18 +2603,18 @@
         <v>0</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>17</v>
+      <c r="B28" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>91</v>
@@ -2812,16 +2635,16 @@
         <v>23</v>
       </c>
       <c r="I28" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J28" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" s="2">
-        <v>2</v>
-      </c>
-      <c r="L28" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L28" s="2">
+        <v>0</v>
       </c>
       <c r="M28" s="2">
         <v>0</v>
@@ -2830,21 +2653,21 @@
         <v>0</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>17</v>
+      <c r="B29" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>91</v>
@@ -2862,16 +2685,16 @@
         <v>23</v>
       </c>
       <c r="I29" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J29" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29" s="2">
-        <v>1</v>
-      </c>
-      <c r="L29" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L29" s="2">
+        <v>0</v>
       </c>
       <c r="M29" s="2">
         <v>0</v>
@@ -2880,18 +2703,18 @@
         <v>0</v>
       </c>
       <c r="O29" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>17</v>
+      <c r="B30" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>94</v>
@@ -2912,16 +2735,16 @@
         <v>96</v>
       </c>
       <c r="I30" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J30" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="2">
-        <v>3</v>
-      </c>
-      <c r="L30" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L30" s="2">
+        <v>0</v>
       </c>
       <c r="M30" s="2">
         <v>0</v>
@@ -2930,18 +2753,18 @@
         <v>0</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>17</v>
+      <c r="B31" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>95</v>
@@ -2962,16 +2785,16 @@
         <v>96</v>
       </c>
       <c r="I31" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J31" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K31" s="2">
-        <v>2</v>
-      </c>
-      <c r="L31" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L31" s="2">
+        <v>0</v>
       </c>
       <c r="M31" s="2">
         <v>0</v>
@@ -2980,18 +2803,18 @@
         <v>0</v>
       </c>
       <c r="O31" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>17</v>
+      <c r="B32" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>98</v>
@@ -3012,16 +2835,16 @@
         <v>96</v>
       </c>
       <c r="I32" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J32" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" s="2">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L32" s="2">
+        <v>0</v>
       </c>
       <c r="M32" s="2">
         <v>0</v>
@@ -3030,18 +2853,18 @@
         <v>0</v>
       </c>
       <c r="O32" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>17</v>
+      <c r="B33" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>101</v>
@@ -3062,16 +2885,16 @@
         <v>96</v>
       </c>
       <c r="I33" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J33" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K33" s="2">
-        <v>2</v>
-      </c>
-      <c r="L33" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L33" s="2">
+        <v>0</v>
       </c>
       <c r="M33" s="2">
         <v>0</v>
@@ -3080,18 +2903,18 @@
         <v>0</v>
       </c>
       <c r="O33" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>17</v>
+      <c r="B34" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>101</v>
@@ -3112,16 +2935,16 @@
         <v>96</v>
       </c>
       <c r="I34" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K34" s="2">
-        <v>1</v>
-      </c>
-      <c r="L34" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L34" s="2">
+        <v>0</v>
       </c>
       <c r="M34" s="2">
         <v>0</v>
@@ -3130,18 +2953,18 @@
         <v>0</v>
       </c>
       <c r="O34" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>17</v>
+      <c r="B35" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>103</v>
@@ -3162,16 +2985,16 @@
         <v>96</v>
       </c>
       <c r="I35" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J35" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" s="2">
-        <v>1</v>
-      </c>
-      <c r="L35" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L35" s="2">
+        <v>0</v>
       </c>
       <c r="M35" s="2">
         <v>0</v>
@@ -3180,24 +3003,24 @@
         <v>0</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>17</v>
+      <c r="B36" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>107</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>20</v>
@@ -3212,16 +3035,16 @@
         <v>96</v>
       </c>
       <c r="I36" s="2">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J36" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K36" s="2">
-        <v>2</v>
-      </c>
-      <c r="L36" s="4">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="2">
+        <v>0</v>
       </c>
       <c r="M36" s="2">
         <v>0</v>
@@ -3230,21 +3053,21 @@
         <v>0</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>72</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>17</v>
+      <c r="B37" s="2" t="s">
+        <v>78</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>107</v>
@@ -3262,16 +3085,16 @@
         <v>96</v>
       </c>
       <c r="I37" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J37" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K37" s="2">
-        <v>1</v>
-      </c>
-      <c r="L37" s="4">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="L37" s="2">
+        <v>0</v>
       </c>
       <c r="M37" s="2">
         <v>0</v>
@@ -3280,10 +3103,10 @@
         <v>0</v>
       </c>
       <c r="O37" s="2" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>85</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.25">
@@ -3445,7 +3268,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H324"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -7776,4114 +7599,526 @@
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G167" s="4" t="s">
-        <v>123</v>
+        <v>133</v>
+      </c>
+      <c r="G167" s="6" t="s">
+        <v>232</v>
       </c>
       <c r="H167" s="2" t="s">
-        <v>124</v>
+        <v>233</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G168" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H168" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>140</v>
       </c>
       <c r="H169" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>132</v>
+        <v>236</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G170" s="4" t="s">
-        <v>123</v>
+        <v>237</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H170" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>135</v>
+        <v>239</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G171" s="4" t="s">
-        <v>123</v>
+        <v>187</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="H171" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="H172" s="2" t="s">
-        <v>207</v>
+        <v>241</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>164</v>
+        <v>121</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>165</v>
+        <v>122</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>140</v>
       </c>
       <c r="H173" s="2" t="s">
-        <v>208</v>
+        <v>242</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="G174" s="8" t="s">
         <v>127</v>
       </c>
       <c r="H174" s="2" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G175" s="4" t="s">
-        <v>123</v>
+        <v>136</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H175" s="2" t="s">
-        <v>147</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G176" s="4" t="s">
-        <v>123</v>
+        <v>139</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="H176" s="2" t="s">
-        <v>124</v>
+        <v>245</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>125</v>
+        <v>236</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G177" s="4" t="s">
-        <v>123</v>
+        <v>237</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>130</v>
+        <v>187</v>
       </c>
       <c r="G178" s="8" t="s">
         <v>140</v>
       </c>
       <c r="H178" s="2" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>61</v>
+        <v>116</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G179" s="4" t="s">
-        <v>123</v>
+        <v>146</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G180" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="H180" s="2" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="H181" s="2" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="H182" s="2" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="H183" s="2" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>79</v>
+        <v>117</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>145</v>
+        <v>236</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G184" s="4" t="s">
-        <v>123</v>
+        <v>237</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H184" s="2" t="s">
-        <v>147</v>
+        <v>246</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>121</v>
+        <v>239</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G185" s="4" t="s">
-        <v>123</v>
+        <v>187</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>140</v>
       </c>
       <c r="H185" s="2" t="s">
-        <v>124</v>
+        <v>247</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>23</v>
+        <v>113</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G186" s="4" t="s">
-        <v>123</v>
+        <v>146</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>127</v>
       </c>
       <c r="H186" s="2" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A187" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B187" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D187" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G187" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H187" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A188" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D188" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F188" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G188" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H188" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B189" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D189" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F189" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G189" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H189" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A190" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D190" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F190" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G190" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H190" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A191" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B191" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D191" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F191" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G191" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H191" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B192" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D192" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F192" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G192" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H192" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A193" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B193" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D193" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E193" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F193" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G193" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H193" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A194" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B194" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D194" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F194" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G194" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H194" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B195" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D195" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E195" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F195" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G195" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H195" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A196" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B196" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G196" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H196" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A197" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B197" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F197" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G197" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H197" s="2" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A198" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B198" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G198" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H198" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A199" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B199" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E199" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F199" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G199" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H199" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A200" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B200" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D200" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F200" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G200" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H200" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A201" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B201" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D201" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E201" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F201" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G201" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H201" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A202" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D202" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E202" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F202" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G202" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H202" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D203" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E203" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F203" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G203" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H203" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A204" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D204" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E204" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F204" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G204" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H204" s="2" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A205" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B205" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D205" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E205" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F205" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G205" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H205" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A206" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B206" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D206" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E206" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F206" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G206" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H206" s="2" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A207" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B207" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D207" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F207" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G207" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H207" s="2" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B208" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D208" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E208" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F208" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G208" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H208" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A209" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D209" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E209" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F209" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G209" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H209" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A210" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D210" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E210" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F210" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G210" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H210" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A211" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D211" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E211" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F211" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G211" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H211" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A212" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D212" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E212" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F212" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G212" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H212" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A213" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B213" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D213" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E213" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F213" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G213" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H213" s="2" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A214" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B214" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D214" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E214" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G214" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H214" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A215" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B215" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E215" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F215" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G215" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H215" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A216" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D216" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E216" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F216" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G216" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H216" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A217" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B217" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D217" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E217" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F217" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G217" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H217" s="2" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A218" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B218" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D218" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E218" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F218" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G218" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H218" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A219" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B219" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D219" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E219" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F219" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G219" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H219" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A220" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B220" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E220" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F220" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G220" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H220" s="2" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A221" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B221" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E221" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F221" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G221" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H221" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A222" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B222" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D222" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E222" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F222" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G222" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H222" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A223" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B223" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D223" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E223" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F223" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G223" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H223" s="2" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A224" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B224" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D224" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E224" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F224" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G224" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H224" s="2" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A225" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B225" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D225" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E225" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F225" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G225" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H225" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A226" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B226" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D226" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E226" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F226" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G226" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H226" s="2" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D227" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E227" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F227" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G227" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H227" s="2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A228" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B228" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D228" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E228" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G228" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H228" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A229" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B229" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G229" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H229" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B230" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D230" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E230" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G230" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H230" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D231" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E231" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G231" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H231" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A232" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B232" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D232" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G232" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H232" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A233" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B233" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D233" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E233" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G233" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H233" s="2" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A234" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B234" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D234" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G234" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H234" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A235" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B235" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D235" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E235" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G235" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H235" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A236" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D236" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G236" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H236" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A237" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B237" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E237" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G237" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H237" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A238" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C238" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D238" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E238" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G238" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H238" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A239" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B239" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C239" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D239" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E239" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G239" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H239" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A240" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C240" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D240" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E240" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G240" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H240" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A241" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D241" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E241" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G241" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H241" s="2" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A242" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D242" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E242" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F242" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G242" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H242" s="2" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A243" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C243" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D243" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E243" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F243" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G243" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H243" s="2" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A244" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D244" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E244" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F244" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G244" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H244" s="2" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A245" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C245" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D245" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E245" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F245" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G245" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H245" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A246" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C246" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D246" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E246" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F246" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G246" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H246" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A247" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C247" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D247" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E247" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F247" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G247" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H247" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A248" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B248" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D248" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E248" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F248" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G248" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H248" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A249" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D249" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E249" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F249" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G249" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H249" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A250" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C250" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D250" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E250" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F250" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G250" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H250" s="2" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A251" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D251" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E251" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F251" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G251" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H251" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A252" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D252" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E252" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F252" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G252" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H252" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A253" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C253" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D253" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F253" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G253" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H253" s="2" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A254" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B254" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C254" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E254" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F254" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G254" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H254" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A255" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B255" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C255" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D255" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E255" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F255" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G255" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H255" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A256" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D256" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E256" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F256" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G256" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H256" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A257" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D257" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E257" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F257" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G257" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H257" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A258" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B258" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C258" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D258" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E258" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F258" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G258" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H258" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A259" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B259" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C259" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D259" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E259" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F259" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G259" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H259" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A260" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B260" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C260" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D260" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E260" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F260" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G260" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H260" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D261" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E261" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F261" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G261" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H261" s="2" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A262" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B262" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C262" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D262" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E262" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F262" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G262" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H262" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A263" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B263" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C263" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D263" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E263" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F263" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G263" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H263" s="2" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A264" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D264" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E264" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F264" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G264" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H264" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A265" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D265" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E265" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F265" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G265" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H265" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A266" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D266" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E266" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F266" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G266" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H266" s="2" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A267" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D267" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E267" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F267" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G267" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H267" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A268" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D268" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E268" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F268" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G268" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H268" s="2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A269" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B269" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E269" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F269" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G269" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H269" s="2" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A270" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B270" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D270" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E270" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F270" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G270" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H270" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A271" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B271" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E271" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F271" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G271" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H271" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A272" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G272" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H272" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A273" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G273" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H273" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A274" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G274" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H274" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B275" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D275" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E275" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F275" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G275" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H275" s="2" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A276" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B276" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D276" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E276" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F276" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G276" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H276" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A277" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G277" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H277" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A278" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D278" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E278" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F278" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G278" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H278" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A279" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B279" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D279" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E279" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F279" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G279" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H279" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A280" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B280" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D280" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E280" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F280" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G280" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H280" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A281" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="B281" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D281" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E281" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F281" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G281" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H281" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A282" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B282" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C282" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D282" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E282" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F282" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G282" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H282" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A283" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C283" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D283" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E283" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F283" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G283" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H283" s="2" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A284" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D284" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E284" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="F284" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G284" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H284" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A285" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C285" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D285" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E285" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F285" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G285" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H285" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A286" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C286" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D286" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E286" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F286" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G286" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H286" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A287" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C287" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D287" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E287" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F287" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G287" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H287" s="2" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A288" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C288" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D288" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E288" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F288" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G288" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H288" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A289" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D289" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E289" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F289" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G289" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H289" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A290" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G290" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H290" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A291" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C291" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D291" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G291" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H291" s="2" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A292" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C292" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D292" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G292" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H292" s="2" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A293" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D293" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G293" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H293" s="2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A294" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C294" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D294" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G294" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H294" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A295" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D295" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E295" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F295" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G295" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H295" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A296" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D296" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E296" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F296" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G296" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H296" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A297" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D297" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E297" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F297" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G297" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H297" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A298" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D298" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E298" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F298" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="G298" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H298" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A299" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G299" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H299" s="2" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G300" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H300" s="2" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A301" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G301" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H301" s="2" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A302" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B302" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C302" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D302" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E302" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F302" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G302" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H302" s="2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A303" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D303" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E303" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F303" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G303" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H303" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A304" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B304" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D304" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E304" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F304" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G304" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="H304" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A305" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C305" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D305" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E305" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F305" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G305" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H305" s="2" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A306" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G306" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H306" s="2" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A307" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B307" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C307" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D307" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E307" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F307" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G307" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H307" s="2" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A308" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D308" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E308" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F308" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G308" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H308" s="2" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A309" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D309" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E309" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F309" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G309" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H309" s="2" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A310" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B310" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C310" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="D310" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E310" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F310" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G310" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H310" s="2" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A311" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B311" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C311" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D311" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E311" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F311" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G311" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H311" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A312" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B312" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D312" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E312" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F312" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G312" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H312" s="2" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A313" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D313" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E313" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F313" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G313" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H313" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A314" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D314" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E314" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F314" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G314" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H314" s="2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A315" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D315" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E315" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F315" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G315" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H315" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A316" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C316" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D316" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E316" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F316" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G316" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H316" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A317" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="D317" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E317" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F317" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G317" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H317" s="2" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A318" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C318" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D318" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E318" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F318" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="G318" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H318" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A319" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C319" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D319" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E319" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F319" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G319" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H319" s="2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A320" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D320" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E320" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F320" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G320" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H320" s="2" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A321" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C321" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D321" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E321" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F321" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G321" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H321" s="2" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A322" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C322" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D322" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E322" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F322" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="G322" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H322" s="2" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A323" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B323" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C323" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D323" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E323" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F323" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="G323" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="H323" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A324" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B324" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C324" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D324" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E324" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F324" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="G324" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="H324" s="2" t="s">
-        <v>312</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H324"/>
+  <autoFilter ref="A1:H186"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -11919,7 +8154,7 @@
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>313</v>
+        <v>254</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -12393,16 +8628,16 @@
         <v>77</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F22" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -12413,19 +8648,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>61</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F23" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -12436,19 +8671,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F24" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -12459,19 +8694,19 @@
         <v>23</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F25" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -12488,13 +8723,13 @@
         <v>87</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F26" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -12511,13 +8746,13 @@
         <v>89</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F27" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -12537,10 +8772,10 @@
         <v>89</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F28" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -12554,16 +8789,16 @@
         <v>92</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>91</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F29" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -12583,10 +8818,10 @@
         <v>95</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F30" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -12606,10 +8841,10 @@
         <v>98</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F31" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -12629,10 +8864,10 @@
         <v>95</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F32" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>20</v>
@@ -12652,10 +8887,10 @@
         <v>98</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F33" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -12675,10 +8910,10 @@
         <v>103</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F34" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -12698,10 +8933,10 @@
         <v>105</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F35" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -12718,13 +8953,13 @@
         <v>107</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F36" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -12738,16 +8973,16 @@
         <v>108</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>107</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="F37" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
